--- a/Input Data Tables/Airline Codes.xlsx
+++ b/Input Data Tables/Airline Codes.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andyeske/Desktop/APAT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andyeske/Desktop/Research/APAT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBC719A8-127C-A647-BE1F-F85421759B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F211285E-6411-7147-8AB0-05148D565AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1900" yWindow="1820" windowWidth="27240" windowHeight="16360" xr2:uid="{A91CC563-155C-0741-B56B-ECF7486E7B62}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>FAA Airline Code</t>
   </si>
@@ -174,6 +174,12 @@
   </si>
   <si>
     <t>G7</t>
+  </si>
+  <si>
+    <t>Avelo</t>
+  </si>
+  <si>
+    <t>XP</t>
   </si>
 </sst>
 </file>
@@ -548,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{798096B7-9980-5C44-A7B8-6A0ABB01F7BF}">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.83203125" customWidth="1"/>
@@ -589,153 +595,161 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>20</v>
       </c>
     </row>

--- a/Input Data Tables/Airline Codes.xlsx
+++ b/Input Data Tables/Airline Codes.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andyeske/Desktop/Research/APAT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andyeske/Desktop/Research/ADAT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F211285E-6411-7147-8AB0-05148D565AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC136B7-EDE5-0748-95F5-3183C8E83B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1820" windowWidth="27240" windowHeight="16360" xr2:uid="{A91CC563-155C-0741-B56B-ECF7486E7B62}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="15680" windowHeight="17420" activeTab="1" xr2:uid="{A91CC563-155C-0741-B56B-ECF7486E7B62}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Current" sheetId="1" r:id="rId1"/>
+    <sheet name="Historical" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="125">
   <si>
     <t>FAA Airline Code</t>
   </si>
@@ -180,6 +181,237 @@
   </si>
   <si>
     <t>XP</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Regional</t>
+  </si>
+  <si>
+    <t>Executive</t>
+  </si>
+  <si>
+    <t>OW</t>
+  </si>
+  <si>
+    <t>Aloha</t>
+  </si>
+  <si>
+    <t>AQ</t>
+  </si>
+  <si>
+    <t>Continental</t>
+  </si>
+  <si>
+    <t>CO</t>
+  </si>
+  <si>
+    <t>US Airways</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>Eastern</t>
+  </si>
+  <si>
+    <t>EA</t>
+  </si>
+  <si>
+    <t>PA (1)</t>
+  </si>
+  <si>
+    <t>Pan Am</t>
+  </si>
+  <si>
+    <t>Northwest</t>
+  </si>
+  <si>
+    <t>NW</t>
+  </si>
+  <si>
+    <t>Air Wisconsin</t>
+  </si>
+  <si>
+    <t>ZW</t>
+  </si>
+  <si>
+    <t>America West</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>TW</t>
+  </si>
+  <si>
+    <t>TWA</t>
+  </si>
+  <si>
+    <t>Virgin America</t>
+  </si>
+  <si>
+    <t>VX</t>
+  </si>
+  <si>
+    <t>Colgan Air</t>
+  </si>
+  <si>
+    <t>9L</t>
+  </si>
+  <si>
+    <t>Reno Air</t>
+  </si>
+  <si>
+    <t>QQ</t>
+  </si>
+  <si>
+    <t>Outcome</t>
+  </si>
+  <si>
+    <t>Merged with US Airways</t>
+  </si>
+  <si>
+    <t>Merged with United</t>
+  </si>
+  <si>
+    <t>Ceased operations</t>
+  </si>
+  <si>
+    <t>Merged with Delta</t>
+  </si>
+  <si>
+    <t>Merged with American</t>
+  </si>
+  <si>
+    <t>Morris Air</t>
+  </si>
+  <si>
+    <t>KN</t>
+  </si>
+  <si>
+    <t>Merged with Southwest</t>
+  </si>
+  <si>
+    <t>AirTran</t>
+  </si>
+  <si>
+    <t>FL</t>
+  </si>
+  <si>
+    <t>ValuJet</t>
+  </si>
+  <si>
+    <t>J7</t>
+  </si>
+  <si>
+    <t>Merged with AirTran</t>
+  </si>
+  <si>
+    <t>EV</t>
+  </si>
+  <si>
+    <t>ASA</t>
+  </si>
+  <si>
+    <t>Merged with ExpressJet</t>
+  </si>
+  <si>
+    <t>ExpressJet</t>
+  </si>
+  <si>
+    <t>Merged with SkyWest</t>
+  </si>
+  <si>
+    <t>Midway</t>
+  </si>
+  <si>
+    <t>JI</t>
+  </si>
+  <si>
+    <t>Merged with Alaska</t>
+  </si>
+  <si>
+    <t>Mesaba</t>
+  </si>
+  <si>
+    <t>XJ</t>
+  </si>
+  <si>
+    <t>Merged with Endeavor</t>
+  </si>
+  <si>
+    <t>ATA</t>
+  </si>
+  <si>
+    <t>TZ</t>
+  </si>
+  <si>
+    <t>Comair</t>
+  </si>
+  <si>
+    <t>Chautauqua</t>
+  </si>
+  <si>
+    <t>RP</t>
+  </si>
+  <si>
+    <t>Merged with Republic</t>
+  </si>
+  <si>
+    <t>Trans States</t>
+  </si>
+  <si>
+    <t>AX</t>
+  </si>
+  <si>
+    <t>XE (1)</t>
+  </si>
+  <si>
+    <t>Subsidiary</t>
+  </si>
+  <si>
+    <t>AA, CO, DL, UA</t>
+  </si>
+  <si>
+    <t>AA, HP, UA, US</t>
+  </si>
+  <si>
+    <t>DL, NW, US</t>
+  </si>
+  <si>
+    <t>AA, DL, UA, US</t>
+  </si>
+  <si>
+    <t>AA, AS, DL, UA, US</t>
+  </si>
+  <si>
+    <t>TWA, UA, US</t>
+  </si>
+  <si>
+    <t>CO, US, UA</t>
+  </si>
+  <si>
+    <t>AA, CO, DL, HP,  TWA, UA</t>
+  </si>
+  <si>
+    <t>AA, UA, US</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>OE</t>
   </si>
 </sst>
 </file>
@@ -554,203 +786,960 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{798096B7-9980-5C44-A7B8-6A0ABB01F7BF}">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.83203125" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C1" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C3" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C4" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C5" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C6" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C7" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C8" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C9" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C10" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C11" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C12" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C13" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C14" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C15" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C16" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C17" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C18" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C19" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C20" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C21" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C22" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C23" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2B6A39C-6A29-F546-A44A-CF82493373F3}">
+  <dimension ref="A1:E49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16.5" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" customWidth="1"/>
+    <col min="4" max="4" width="23" customWidth="1"/>
+    <col min="5" max="5" width="22.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
